--- a/docs/deliverables/out/Programme/FitGap/BIBS_FitGap_BRD-01_New_Business_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/FitGap/BIBS_FitGap_BRD-01_New_Business_BRD_vs_OOTB_vs_Best_Practice_v1.0.xlsx
@@ -32,7 +32,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,11 @@
       <name val="Arial"/>
       <color rgb="00656565"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00616161"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -182,25 +187,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,10 +213,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +230,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -836,7 +844,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Counts of the Fit-Gap sheet; 118 rows in scope.</t>
+          <t>Counts of the Fit-Gap sheet; 115 rows in scope.</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -3675,76 +3683,76 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="12" t="inlineStr">
+      <c r="A71" s="22" t="inlineStr">
         <is>
           <t>BRNB.067</t>
         </is>
       </c>
-      <c r="B71" s="12" t="inlineStr">
+      <c r="B71" s="22" t="inlineStr">
         <is>
           <t>FR-NB-090, FR-NB-091</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr">
+      <c r="C71" s="22" t="inlineStr">
         <is>
           <t>Generate the CLPC billing file (CBG Fire)</t>
         </is>
       </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>Extend</t>
-        </is>
-      </c>
-      <c r="F71" s="12" t="inlineStr">
+      <c r="D71" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F71" s="22" t="inlineStr">
         <is>
           <t>QPL-024, INT-009</t>
         </is>
       </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t>Bank statement import and matching exist; no loan billing file. A bank interface would be a change request.; No loan-system interface. BIBS screens: SCR-NB-21, SCR-NB-22.</t>
+      <c r="G71" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-NB-21, SCR-NB-22.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="12" t="inlineStr">
+      <c r="A72" s="22" t="inlineStr">
         <is>
           <t>BRNB.068</t>
         </is>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="22" t="inlineStr">
         <is>
           <t>FR-NB-091, FR-NB-092</t>
         </is>
       </c>
-      <c r="C72" s="12" t="inlineStr">
+      <c r="C72" s="22" t="inlineStr">
         <is>
           <t>Match payment reports (CLPC and other segments)</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Extend</t>
-        </is>
-      </c>
-      <c r="F72" s="12" t="inlineStr">
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F72" s="22" t="inlineStr">
         <is>
           <t>QPL-023, QPL-024</t>
         </is>
       </c>
-      <c r="G72" s="12" t="inlineStr">
-        <is>
-          <t>No payment condition on placement; claims can be blocked while premium is unpaid.; Bank statement import and matching exist; no loan billing file. A bank interface would be a change request. BIBS screens: SCR-NB-19, SCR-NB-21, SCR-NB-22.</t>
+      <c r="G72" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-NB-19, SCR-NB-21, SCR-NB-22.</t>
         </is>
       </c>
     </row>
@@ -5562,148 +5570,148 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="A122" s="23" t="inlineStr">
         <is>
           <t>OOS-1</t>
         </is>
       </c>
-      <c r="B122" s="22" t="inlineStr">
+      <c r="B122" s="23" t="inlineStr">
         <is>
           <t>Section 1.2 (out of scope)</t>
         </is>
       </c>
-      <c r="C122" s="22" t="inlineStr">
+      <c r="C122" s="23" t="inlineStr">
         <is>
           <t>(line removed from the BRD)</t>
         </is>
       </c>
-      <c r="D122" s="22" t="inlineStr">
+      <c r="D122" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E122" s="23" t="inlineStr">
         <is>
           <t>Removed from the BRD</t>
         </is>
       </c>
-      <c r="F122" s="22" t="inlineStr">
+      <c r="F122" s="23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="22" t="inlineStr">
+      <c r="G122" s="23" t="inlineStr">
         <is>
           <t>Removed from the BRD by BDOI; no delivery.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>OOS-2</t>
         </is>
       </c>
-      <c r="B123" s="12" t="inlineStr">
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>FR-NB-047, FR-NB-090</t>
         </is>
       </c>
-      <c r="C123" s="12" t="inlineStr">
+      <c r="C123" s="22" t="inlineStr">
         <is>
           <t>One Account Reference Number from quotation to invoice</t>
         </is>
       </c>
-      <c r="D123" s="12" t="inlineStr">
-        <is>
-          <t>Black (BRD)</t>
-        </is>
-      </c>
-      <c r="E123" s="12" t="inlineStr">
-        <is>
-          <t>Extend</t>
-        </is>
-      </c>
-      <c r="F123" s="12" t="inlineStr">
+      <c r="D123" s="22" t="inlineStr">
+        <is>
+          <t>Grey (Integration)</t>
+        </is>
+      </c>
+      <c r="E123" s="22" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="F123" s="22" t="inlineStr">
         <is>
           <t>POL-001, QPL-024</t>
         </is>
       </c>
-      <c r="G123" s="12" t="inlineStr">
-        <is>
-          <t>Each step has its own number (QT-, PS-, POL-, INV-) linked to each other; no single reference carried on every record.; Bank statement import and matching exist; no loan billing file. A bank interface would be a change request. BIBS screens: SCR-NB-15, SCR-NB-40.</t>
+      <c r="G123" s="22" t="inlineStr">
+        <is>
+          <t>Depends on an interface with another BDO or third-party system; Integration scope. BIBS screens: SCR-NB-15, SCR-NB-40.</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="23" t="inlineStr">
+      <c r="A124" s="24" t="inlineStr">
         <is>
           <t>CRM-027</t>
         </is>
       </c>
-      <c r="B124" s="23" t="inlineStr">
+      <c r="B124" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
+      <c r="C124" s="24" t="inlineStr">
         <is>
           <t>Client portal: Let clients view their policies, documents, bills and service requests online.</t>
         </is>
       </c>
-      <c r="D124" s="23" t="inlineStr">
+      <c r="D124" s="24" t="inlineStr">
         <is>
           <t>Blue (best practice)</t>
         </is>
       </c>
-      <c r="E124" s="23" t="inlineStr">
+      <c r="E124" s="24" t="inlineStr">
         <is>
           <t>Best practice</t>
         </is>
       </c>
-      <c r="F124" s="23" t="inlineStr">
+      <c r="F124" s="24" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="G124" s="23" t="inlineStr">
+      <c r="G124" s="24" t="inlineStr">
         <is>
           <t>Brokers increasingly offer a secure client portal or app for policy documents, renewals and requests.</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="23" t="inlineStr">
+      <c r="A125" s="24" t="inlineStr">
         <is>
           <t>CRM-028</t>
         </is>
       </c>
-      <c r="B125" s="23" t="inlineStr">
+      <c r="B125" s="24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
+      <c r="C125" s="24" t="inlineStr">
         <is>
           <t>Client groups and related parties: Link related clients (corporate groups, family members) to view and manage the relationship as a whole.</t>
         </is>
       </c>
-      <c r="D125" s="23" t="inlineStr">
+      <c r="D125" s="24" t="inlineStr">
         <is>
           <t>Blue (best practice)</t>
         </is>
       </c>
-      <c r="E125" s="23" t="inlineStr">
+      <c r="E125" s="24" t="inlineStr">
         <is>
           <t>Best practice</t>
         </is>
       </c>
-      <c r="F125" s="23" t="inlineStr">
+      <c r="F125" s="24" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="G125" s="23" t="inlineStr">
+      <c r="G125" s="24" t="inlineStr">
         <is>
           <t>Corporate group structures are held so total exposure, revenue and service can be managed per group.</t>
         </is>
@@ -5763,7 +5771,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Counts of the Fit-Gap sheet; 118 rows in scope.</t>
+          <t>Counts of the Fit-Gap sheet; 115 rows in scope.</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5834,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
@@ -5856,7 +5864,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
@@ -5931,7 +5939,7 @@
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
@@ -6101,70 +6109,70 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>Fit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Configure</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Extend</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>Recommend change</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Integration scope</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Data Migration scope</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Removed from the BRD</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>Specified in another FRS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Best practice</t>
         </is>
